--- a/public/gisung.xlsx
+++ b/public/gisung.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProject\MyProject\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1b8c881c71dd5844/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CA73BC-0761-4007-A0D9-7C95112C5025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="8_{0156B002-BCBC-4437-83BD-6094AE15FCAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3865AC55-C502-4F16-94ED-C4DEEC6F3FC3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="893" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="893" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="갑지" sheetId="67" r:id="rId1"/>
@@ -40,7 +40,7 @@
     <definedName name="HTML_PathFile">"C:\내작업철\견적양식\MyHTML.htm"</definedName>
     <definedName name="HTML_Title">"견적서"</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">갑지!$A$1:$J$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'기성금 내역서'!$A$1:$M$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'기성금 내역서'!$A$1:$M$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'기성금 내역서'!$1:$4</definedName>
     <definedName name="solver_drv">1</definedName>
     <definedName name="solver_est">1</definedName>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="54">
   <si>
     <t/>
   </si>
@@ -97,6 +97,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>선급금</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>계 약 금 액</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -122,6 +126,18 @@
   </si>
   <si>
     <t>유리공사</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>총원가</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>부가가치세</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>총   계</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -270,7 +286,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>기성금 청구서</t>
+    <t>0차 기성금 청구서</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -281,7 +297,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0.0######"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -355,6 +371,12 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="돋움"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -370,6 +392,13 @@
       <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
@@ -445,8 +474,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="돋움"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -464,8 +507,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -490,12 +539,83 @@
     </border>
     <border>
       <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="medium">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="medium">
+        <color indexed="8"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -510,28 +630,288 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
       <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="medium">
+        <color indexed="8"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="8"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="medium">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
+      <bottom style="medium">
+        <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -555,7 +935,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -563,15 +943,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="3" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="3" applyFont="1">
@@ -583,43 +954,43 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="11"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="11"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
@@ -642,65 +1013,223 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="11"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="4" borderId="18" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="15" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="13" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -715,38 +1244,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="13"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -770,65 +1303,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>16731</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>654326</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>16731</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2050" name="_x115646424">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8742AD41-8003-456F-88FC-8AF93237487C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeShapeType="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="0" y="4754383"/>
-          <a:ext cx="6170543" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="17780">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:noFill/>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2554,7 +3028,7 @@
   <dimension ref="A2:L44"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.5" style="16" customWidth="1"/>
+    <col min="1" max="1" width="3.5" style="13" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="1.625" customWidth="1"/>
     <col min="4" max="4" width="17.125" bestFit="1" customWidth="1"/>
@@ -2567,584 +3041,599 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="15"/>
+      <c r="A2" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
+      <c r="A4" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="30"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="17"/>
+      <c r="A6" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="87"/>
+      <c r="H6" s="87"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="14"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="30"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
+      <c r="A8" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="88"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="30"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="20"/>
+      <c r="A10" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="89" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="89"/>
+      <c r="F10" s="89"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="89"/>
+      <c r="J10" s="89"/>
+      <c r="K10" s="17"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="30"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="20"/>
+      <c r="A12" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="89" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="89"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="89"/>
+      <c r="H12" s="89"/>
+      <c r="I12" s="89"/>
+      <c r="J12" s="89"/>
+      <c r="K12" s="17"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="30"/>
-      <c r="C13" s="31"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="26"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="47" t="str">
+      <c r="A14" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="90" t="str">
         <f>"일금 "&amp;(NUMBERSTRING(H14,1)&amp;"원정")</f>
         <v>일금 영원정</v>
       </c>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
+      <c r="E14" s="90"/>
+      <c r="F14" s="90"/>
       <c r="G14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="35">
-        <f>'기성금 내역서'!F28</f>
+        <v>21</v>
+      </c>
+      <c r="H14" s="30">
+        <f>'기성금 내역서'!F29</f>
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="30"/>
-      <c r="C15" s="31"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="47" t="str">
+      <c r="A16" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="90" t="str">
         <f>"일금 "&amp;(NUMBERSTRING(H16,1)&amp;"원정")</f>
         <v>일금 영원정</v>
       </c>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="90"/>
       <c r="G16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" s="35">
-        <f>'기성금 내역서'!H25</f>
+        <v>21</v>
+      </c>
+      <c r="H16" s="30">
+        <f>'기성금 내역서'!H26</f>
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J16" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="36"/>
-      <c r="C17" s="33"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="32" t="s">
+      <c r="A18" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="47" t="str">
+      <c r="C18" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="90" t="str">
         <f>"일금 "&amp;(NUMBERSTRING(H18,1)&amp;"원정")</f>
         <v>일금 영원정</v>
       </c>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
       <c r="G18" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" s="35">
-        <f>'기성금 내역서'!H28</f>
+        <v>21</v>
+      </c>
+      <c r="H18" s="30">
+        <f>'기성금 내역서'!H29</f>
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="30"/>
-      <c r="C19" s="31"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="26"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="32" t="s">
+      <c r="A20" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="47" t="str">
+      <c r="C20" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="90" t="str">
         <f>"일금 "&amp;(NUMBERSTRING(H20,1)&amp;"원정")</f>
         <v>일금 영원정</v>
       </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
       <c r="G20" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" s="35">
-        <f>'기성금 내역서'!J28</f>
+        <v>21</v>
+      </c>
+      <c r="H20" s="30">
+        <f>'기성금 내역서'!J29</f>
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="37"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="78"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="30"/>
-      <c r="C22" s="31"/>
+      <c r="A22" s="81"/>
+      <c r="B22" s="82"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="47" t="str">
+      <c r="A23" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="90" t="str">
         <f>"일금 "&amp;(NUMBERSTRING(H23,1)&amp;"원정")</f>
         <v>일금 영원정</v>
       </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
+      <c r="E23" s="90"/>
+      <c r="F23" s="90"/>
       <c r="G23" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" s="35">
-        <f>'기성금 내역서'!L28</f>
+        <v>21</v>
+      </c>
+      <c r="H23" s="30">
+        <f>'기성금 내역서'!L29</f>
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J23" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B24" s="30"/>
-      <c r="C24" s="31"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="26"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>15</v>
+      <c r="A25" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B26" s="30"/>
-      <c r="C26" s="31"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="26"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="47" t="str">
+      <c r="A27" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="90" t="str">
         <f>"일금 "&amp;(NUMBERSTRING(H27,1)&amp;"원정")</f>
         <v>일금 영원정</v>
       </c>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
+      <c r="E27" s="90"/>
+      <c r="F27" s="90"/>
       <c r="G27" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="30">
+        <f>'기성금 내역서'!F29-'기성금 내역서'!L29</f>
+        <v>0</v>
+      </c>
+      <c r="I27" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B28" s="25"/>
+      <c r="C28" s="26"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="25"/>
+      <c r="C30" s="26"/>
+    </row>
+    <row r="31" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="86" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="86"/>
+      <c r="C31" s="86"/>
+      <c r="D31" s="86"/>
+      <c r="E31" s="86"/>
+      <c r="F31" s="86"/>
+      <c r="G31" s="86"/>
+      <c r="H31" s="86"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="86"/>
+      <c r="K31" s="16"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="86"/>
+      <c r="B32" s="86"/>
+      <c r="C32" s="86"/>
+      <c r="D32" s="86"/>
+      <c r="E32" s="86"/>
+      <c r="F32" s="86"/>
+      <c r="G32" s="86"/>
+      <c r="H32" s="86"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="86"/>
+      <c r="K32" s="16"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="86"/>
+      <c r="B33" s="86"/>
+      <c r="C33" s="86"/>
+      <c r="D33" s="86"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="86"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="16"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="86"/>
+      <c r="B34" s="86"/>
+      <c r="C34" s="86"/>
+      <c r="D34" s="86"/>
+      <c r="E34" s="86"/>
+      <c r="F34" s="86"/>
+      <c r="G34" s="86"/>
+      <c r="H34" s="86"/>
+      <c r="I34" s="86"/>
+      <c r="J34" s="86"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="6"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="91" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="91"/>
+      <c r="C36" s="91"/>
+      <c r="D36" s="91"/>
+      <c r="E36" s="91"/>
+      <c r="F36" s="91"/>
+      <c r="G36" s="91"/>
+      <c r="H36" s="91"/>
+      <c r="I36" s="91"/>
+      <c r="J36" s="91"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="7"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="7"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C38" s="24"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="92" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" s="92"/>
+      <c r="C39" s="92"/>
+      <c r="D39" s="92"/>
+      <c r="E39" s="92"/>
+      <c r="F39" s="92"/>
+      <c r="G39" s="92"/>
+      <c r="H39" s="92"/>
+      <c r="I39" s="92"/>
+      <c r="J39" s="92"/>
+      <c r="K39" s="14"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="H27" s="35">
-        <f>'기성금 내역서'!F28-'기성금 내역서'!L28</f>
-        <v>0</v>
-      </c>
-      <c r="I27" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B28" s="30"/>
-      <c r="C28" s="31"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B30" s="30"/>
-      <c r="C30" s="31"/>
-    </row>
-    <row r="31" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="43"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="19"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="43"/>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="43"/>
-      <c r="J32" s="43"/>
-      <c r="K32" s="19"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="43"/>
-      <c r="B33" s="43"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="43"/>
-      <c r="I33" s="43"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="19"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="43"/>
-      <c r="B34" s="43"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
-      <c r="J34" s="43"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="9"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="9"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="10"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="10"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C38" s="29"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="49"/>
-      <c r="C39" s="49"/>
-      <c r="D39" s="49"/>
-      <c r="E39" s="49"/>
-      <c r="F39" s="49"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-      <c r="K39" s="17"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="49"/>
-      <c r="C40" s="49"/>
-      <c r="D40" s="49"/>
-      <c r="E40" s="49"/>
-      <c r="F40" s="49"/>
-      <c r="G40" s="49"/>
-      <c r="H40" s="49"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="49"/>
-      <c r="K40" s="17"/>
+      <c r="B40" s="92"/>
+      <c r="C40" s="92"/>
+      <c r="D40" s="92"/>
+      <c r="E40" s="92"/>
+      <c r="F40" s="92"/>
+      <c r="G40" s="92"/>
+      <c r="H40" s="92"/>
+      <c r="I40" s="92"/>
+      <c r="J40" s="92"/>
+      <c r="K40" s="14"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="B41" s="49"/>
-      <c r="C41" s="49"/>
-      <c r="D41" s="49"/>
-      <c r="E41" s="49"/>
-      <c r="F41" s="49"/>
-      <c r="G41" s="49"/>
-      <c r="H41" s="49"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="49"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="11"/>
+      <c r="A41" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" s="92"/>
+      <c r="C41" s="92"/>
+      <c r="D41" s="92"/>
+      <c r="E41" s="92"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="92"/>
+      <c r="H41" s="92"/>
+      <c r="I41" s="92"/>
+      <c r="J41" s="92"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="8"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L42" s="12"/>
+      <c r="L42" s="9"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L43" s="12"/>
+      <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A44" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="B44" s="50"/>
-      <c r="C44" s="50"/>
-      <c r="D44" s="50"/>
-      <c r="E44" s="50"/>
-      <c r="F44" s="50"/>
-      <c r="G44" s="50"/>
-      <c r="H44" s="50"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="21"/>
+      <c r="A44" s="93" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="93"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
+      <c r="F44" s="93"/>
+      <c r="G44" s="93"/>
+      <c r="H44" s="93"/>
+      <c r="I44" s="93"/>
+      <c r="J44" s="93"/>
+      <c r="K44" s="18"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0"/>
@@ -3177,7 +3666,6 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="46" max="16383" man="1"/>
   </rowBreaks>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3186,7 +3674,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.75" style="2" customWidth="1"/>
@@ -3198,915 +3686,1000 @@
     <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-    </row>
-    <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="str">
+    <row r="1" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="95" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+    </row>
+    <row r="2" spans="1:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="102" t="str">
         <f>"공사명 : "&amp;갑지!D4&amp;" 중 유리공사"</f>
         <v>공사명 :  중 유리공사</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
+      <c r="B2" s="102"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="102"/>
     </row>
     <row r="3" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="97" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="94" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="94" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="51" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="51" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51" t="s">
+      <c r="F3" s="94"/>
+      <c r="G3" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51" t="s">
+      <c r="H3" s="94"/>
+      <c r="I3" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51" t="s">
+      <c r="J3" s="94"/>
+      <c r="K3" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51" t="s">
+      <c r="L3" s="94"/>
+      <c r="M3" s="100" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="20.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="98"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="77" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="77" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="77" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="39" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="39" t="s">
+      <c r="H4" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="39" t="s">
+      <c r="I4" s="77" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="39" t="s">
+      <c r="K4" s="77" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="L4" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="55"/>
+      <c r="M4" s="101"/>
     </row>
     <row r="5" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="L5" s="25"/>
-      <c r="M5" s="22" t="s">
+      <c r="A5" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="L5" s="46"/>
+      <c r="M5" s="47" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="24">
-        <f t="shared" ref="F6" si="0">D6*E6</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="25"/>
-      <c r="H6" s="24">
+      <c r="A6" s="37"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="21">
+        <f t="shared" ref="F6:F13" si="0">D6*E6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="22"/>
+      <c r="H6" s="21">
         <f>G6*E6</f>
         <v>0</v>
       </c>
-      <c r="I6" s="25"/>
-      <c r="J6" s="24">
+      <c r="I6" s="22"/>
+      <c r="J6" s="21">
         <f>E6*I6</f>
         <v>0</v>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="22">
         <f>G6+I6</f>
         <v>0</v>
       </c>
-      <c r="L6" s="25">
+      <c r="L6" s="22">
         <f>H6+J6</f>
         <v>0</v>
       </c>
-      <c r="M6" s="41" t="e">
+      <c r="M6" s="48" t="e">
         <f>L6/F6</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="24">
-        <f t="shared" ref="F7:F21" si="1">D7*E7</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="25"/>
-      <c r="H7" s="24">
-        <f t="shared" ref="H7:H21" si="2">G7*E7</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="25"/>
-      <c r="J7" s="24">
-        <f t="shared" ref="J7:J21" si="3">E7*I7</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="25">
-        <f t="shared" ref="K7:K21" si="4">G7+I7</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="25">
-        <f t="shared" ref="L7:L21" si="5">H7+J7</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="41" t="e">
-        <f t="shared" ref="M7:M21" si="6">L7/F7</f>
+      <c r="A7" s="37"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="21">
+        <f t="shared" ref="F7:F25" si="1">D7*E7</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="22"/>
+      <c r="H7" s="21">
+        <f t="shared" ref="H7:H25" si="2">G7*E7</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="22"/>
+      <c r="J7" s="21">
+        <f t="shared" ref="J7:J25" si="3">E7*I7</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="22">
+        <f t="shared" ref="K7:K25" si="4">G7+I7</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="22">
+        <f t="shared" ref="L7:L25" si="5">H7+J7</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="48" t="e">
+        <f t="shared" ref="M7:M25" si="6">L7/F7</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="24">
+      <c r="A8" s="37"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" s="25"/>
-      <c r="H8" s="24">
+      <c r="G8" s="22"/>
+      <c r="H8" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I8" s="25"/>
-      <c r="J8" s="24">
+      <c r="I8" s="22"/>
+      <c r="J8" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M8" s="41" t="e">
+      <c r="M8" s="48" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="24">
+      <c r="A9" s="37"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="24">
+      <c r="G9" s="22"/>
+      <c r="H9" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I9" s="25"/>
-      <c r="J9" s="24">
+      <c r="I9" s="22"/>
+      <c r="J9" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L9" s="25">
+      <c r="L9" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M9" s="41" t="e">
+      <c r="M9" s="48" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="24">
+      <c r="A10" s="37"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G10" s="25"/>
-      <c r="H10" s="24">
+      <c r="G10" s="22"/>
+      <c r="H10" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I10" s="25"/>
-      <c r="J10" s="24">
+      <c r="I10" s="22"/>
+      <c r="J10" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K10" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L10" s="25">
+      <c r="L10" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M10" s="41" t="e">
+      <c r="M10" s="48" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="24">
+      <c r="A11" s="37"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G11" s="25"/>
-      <c r="H11" s="24">
+      <c r="G11" s="22"/>
+      <c r="H11" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I11" s="25"/>
-      <c r="J11" s="24">
+      <c r="I11" s="22"/>
+      <c r="J11" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L11" s="25">
+      <c r="L11" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="41" t="e">
+      <c r="M11" s="48" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="24">
+      <c r="A12" s="37"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G12" s="25"/>
-      <c r="H12" s="24">
+      <c r="G12" s="22"/>
+      <c r="H12" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I12" s="25"/>
-      <c r="J12" s="24">
+      <c r="I12" s="22"/>
+      <c r="J12" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L12" s="25">
+      <c r="L12" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M12" s="41" t="e">
+      <c r="M12" s="48" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="24">
+      <c r="A13" s="37"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G13" s="25"/>
-      <c r="H13" s="24">
+      <c r="G13" s="22"/>
+      <c r="H13" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I13" s="25"/>
-      <c r="J13" s="24">
+      <c r="I13" s="22"/>
+      <c r="J13" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L13" s="25">
+      <c r="L13" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M13" s="41" t="e">
+      <c r="M13" s="48" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="24">
+      <c r="A14" s="37"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G14" s="25"/>
-      <c r="H14" s="24">
+      <c r="G14" s="22"/>
+      <c r="H14" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I14" s="25"/>
-      <c r="J14" s="24">
+      <c r="I14" s="22"/>
+      <c r="J14" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L14" s="25">
+      <c r="L14" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M14" s="41" t="e">
+      <c r="M14" s="48" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="24">
+      <c r="A15" s="37"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G15" s="25"/>
-      <c r="H15" s="24">
+      <c r="G15" s="22"/>
+      <c r="H15" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I15" s="25"/>
-      <c r="J15" s="24">
+      <c r="I15" s="22"/>
+      <c r="J15" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L15" s="25">
+      <c r="L15" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M15" s="41" t="e">
+      <c r="M15" s="48" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="24">
+      <c r="A16" s="37"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G16" s="25"/>
-      <c r="H16" s="24">
+      <c r="G16" s="22"/>
+      <c r="H16" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I16" s="25"/>
-      <c r="J16" s="24">
+      <c r="I16" s="22"/>
+      <c r="J16" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K16" s="25">
+      <c r="K16" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L16" s="25">
+      <c r="L16" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M16" s="41" t="e">
+      <c r="M16" s="48" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="27"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24">
+      <c r="A17" s="37"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="25"/>
-      <c r="H17" s="24">
+      <c r="G17" s="22"/>
+      <c r="H17" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I17" s="25"/>
-      <c r="J17" s="24">
+      <c r="I17" s="22"/>
+      <c r="J17" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L17" s="25">
+      <c r="L17" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M17" s="41" t="e">
+      <c r="M17" s="48" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="27"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24">
+      <c r="A18" s="39"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G18" s="25"/>
-      <c r="H18" s="24">
+      <c r="G18" s="22"/>
+      <c r="H18" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I18" s="25"/>
-      <c r="J18" s="24">
+      <c r="I18" s="22"/>
+      <c r="J18" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K18" s="25">
+      <c r="K18" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L18" s="25">
+      <c r="L18" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M18" s="41" t="e">
+      <c r="M18" s="48" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="27"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24">
+      <c r="A19" s="39"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G19" s="25"/>
-      <c r="H19" s="24">
+      <c r="G19" s="22"/>
+      <c r="H19" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I19" s="25"/>
-      <c r="J19" s="24">
+      <c r="I19" s="22"/>
+      <c r="J19" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K19" s="25">
+      <c r="K19" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L19" s="25">
+      <c r="L19" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M19" s="41" t="e">
+      <c r="M19" s="48" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="27"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24">
+      <c r="A20" s="39"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="25"/>
-      <c r="H20" s="24">
+      <c r="G20" s="22"/>
+      <c r="H20" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I20" s="25"/>
-      <c r="J20" s="24">
+      <c r="I20" s="22"/>
+      <c r="J20" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K20" s="25">
+      <c r="K20" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L20" s="25">
+      <c r="L20" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M20" s="41" t="e">
+      <c r="M20" s="48" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="27"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24">
+      <c r="A21" s="39"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G21" s="25"/>
-      <c r="H21" s="24">
+      <c r="G21" s="22"/>
+      <c r="H21" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I21" s="25"/>
-      <c r="J21" s="24">
+      <c r="I21" s="22"/>
+      <c r="J21" s="21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K21" s="25">
+      <c r="K21" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L21" s="25">
+      <c r="L21" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M21" s="41" t="e">
+      <c r="M21" s="48" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="27"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24">
-        <f t="shared" ref="F22:F27" si="7">D22*E22</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="25"/>
-      <c r="H22" s="24">
-        <f t="shared" ref="H22:H27" si="8">G22*E22</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="25"/>
-      <c r="J22" s="24">
-        <f t="shared" ref="J22:J27" si="9">E22*I22</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="25">
-        <f t="shared" ref="K22:K27" si="10">G22+I22</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="25">
-        <f t="shared" ref="L22:L27" si="11">H22+J22</f>
-        <v>0</v>
-      </c>
-      <c r="M22" s="41" t="e">
-        <f t="shared" ref="M22:M27" si="12">L22/F22</f>
+      <c r="A22" s="39"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="22"/>
+      <c r="H22" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="22"/>
+      <c r="J22" s="21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="22">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="48" t="e">
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="38"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24">
+      <c r="A23" s="39"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="22"/>
+      <c r="H23" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="22"/>
+      <c r="J23" s="21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="22">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="48" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="49"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="22"/>
+      <c r="H24" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="22"/>
+      <c r="J24" s="21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="22">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="48" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="50"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="22"/>
+      <c r="H25" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="22"/>
+      <c r="J25" s="21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="22">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="48" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="76" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="34"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="36"/>
+      <c r="L26" s="36"/>
+      <c r="M26" s="54"/>
+    </row>
+    <row r="27" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="62"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="65">
+        <f>SUM(F6:F25)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="64"/>
+      <c r="H27" s="65">
+        <f>SUM(H6:H25)+F26</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="64"/>
+      <c r="J27" s="65">
+        <f>SUM(J6:J25)</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="64"/>
+      <c r="L27" s="65">
+        <f>SUM(L6:L25)</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="40"/>
+    </row>
+    <row r="28" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="67"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69">
+        <f>F27*0.1</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69">
+        <f>H27*0.1</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="69"/>
+      <c r="J28" s="69">
+        <f>J27*0.1</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="69"/>
+      <c r="L28" s="70">
+        <f t="shared" ref="L7:L29" si="7">H28+J28</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="38"/>
+    </row>
+    <row r="29" spans="1:13" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="71" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="72"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="74">
+        <f>F27+F28</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="74"/>
+      <c r="H29" s="74">
+        <f>SUM(H27:H28)</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="74"/>
+      <c r="J29" s="74">
+        <f>SUM(J27:J28)</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="74"/>
+      <c r="L29" s="75">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G23" s="25"/>
-      <c r="H23" s="24">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="25"/>
-      <c r="J23" s="24">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="25">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="25">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="41" t="e">
-        <f t="shared" si="12"/>
+      <c r="M29" s="41" t="e">
+        <f t="shared" ref="M29" si="8">L29/F29</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="27"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="25"/>
-      <c r="H24" s="24">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="25"/>
-      <c r="J24" s="24">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="25">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="25">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="41" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="27"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="41"/>
-    </row>
-    <row r="26" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="27"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="25"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="25"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="41"/>
-    </row>
-    <row r="27" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="27"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="41"/>
-    </row>
-    <row r="28" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="27"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="25"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="41"/>
-    </row>
-    <row r="29" spans="1:13" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="22"/>
-    </row>
-    <row r="30" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="3"/>
+    <row r="30" spans="1:13" ht="20.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="55"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="58"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="59"/>
+      <c r="K30" s="58"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="60"/>
     </row>
     <row r="31" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="3"/>
     </row>
     <row r="32" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
     </row>
     <row r="33" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
     </row>
     <row r="34" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0"/>
   <protectedRanges>
-    <protectedRange sqref="A2:M2 A6:E21 G6:G28 I6:I28" name="범위1"/>
+    <protectedRange sqref="A2:M2 A6:E22 G6:G26 I6:I26 D23:E26" name="범위1"/>
   </protectedRanges>
   <mergeCells count="11">
     <mergeCell ref="K3:L3"/>

--- a/public/gisung.xlsx
+++ b/public/gisung.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1b8c881c71dd5844/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProject\MyProject\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="8_{0156B002-BCBC-4437-83BD-6094AE15FCAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3865AC55-C502-4F16-94ED-C4DEEC6F3FC3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16234AF-F9AE-4A49-B9FC-316CAD205393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="893" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="893" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="갑지" sheetId="67" r:id="rId1"/>
@@ -97,10 +97,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>선급금</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>계 약 금 액</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -287,6 +283,10 @@
   </si>
   <si>
     <t>0차 기성금 청구서</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>선급금(부가세 별도)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -297,7 +297,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0.0######"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -373,6 +373,12 @@
       <sz val="9"/>
       <name val="돋움"/>
       <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
@@ -514,7 +520,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -689,6 +695,19 @@
       </left>
       <right style="thin">
         <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="8"/>
@@ -935,7 +954,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -954,43 +973,43 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="11"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="11"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
@@ -1013,30 +1032,30 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="11"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="11"/>
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -1045,15 +1064,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1064,17 +1075,17 @@
     <xf numFmtId="9" fontId="2" fillId="2" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="4" borderId="18" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="4" borderId="19" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1094,7 +1105,7 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1102,11 +1113,11 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1114,122 +1125,153 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="13" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="14" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="13"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="15" xfId="3" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="3" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="3" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="13" xfId="3" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1244,17 +1286,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="13"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1267,20 +1298,32 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -3041,18 +3084,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
+      <c r="A2" s="94" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
       <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -3069,21 +3112,21 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
+        <v>18</v>
+      </c>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="25"/>
@@ -3098,21 +3141,21 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="87"/>
-      <c r="E6" s="87"/>
-      <c r="F6" s="87"/>
-      <c r="G6" s="87"/>
-      <c r="H6" s="87"/>
-      <c r="I6" s="87"/>
-      <c r="J6" s="87"/>
+        <v>18</v>
+      </c>
+      <c r="D6" s="96"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="96"/>
+      <c r="H6" s="96"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="96"/>
       <c r="K6" s="14"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -3128,21 +3171,21 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="88"/>
+        <v>18</v>
+      </c>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="97"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="25"/>
@@ -3157,23 +3200,23 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="89" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="89"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="89"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="89"/>
-      <c r="J10" s="89"/>
+        <v>18</v>
+      </c>
+      <c r="D10" s="98" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="98"/>
       <c r="K10" s="17"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -3189,23 +3232,23 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="89" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="89"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="89"/>
-      <c r="H12" s="89"/>
-      <c r="I12" s="89"/>
-      <c r="J12" s="89"/>
+        <v>18</v>
+      </c>
+      <c r="D12" s="98" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="98"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="98"/>
       <c r="K12" s="17"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -3214,32 +3257,32 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="90" t="str">
+        <v>18</v>
+      </c>
+      <c r="D14" s="99" t="str">
         <f>"일금 "&amp;(NUMBERSTRING(H14,1)&amp;"원정")</f>
         <v>일금 영원정</v>
       </c>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H14" s="30">
         <f>'기성금 내역서'!F29</f>
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -3248,32 +3291,29 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="90" t="str">
+        <v>18</v>
+      </c>
+      <c r="D16" s="99" t="str">
         <f>"일금 "&amp;(NUMBERSTRING(H16,1)&amp;"원정")</f>
         <v>일금 영원정</v>
       </c>
-      <c r="E16" s="90"/>
-      <c r="F16" s="90"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="99"/>
       <c r="G16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="90"/>
+      <c r="I16" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" t="s">
         <v>21</v>
-      </c>
-      <c r="H16" s="30">
-        <f>'기성금 내역서'!H26</f>
-        <v>0</v>
-      </c>
-      <c r="I16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -3282,32 +3322,32 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="27" t="s">
         <v>4</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="90" t="str">
+        <v>18</v>
+      </c>
+      <c r="D18" s="99" t="str">
         <f>"일금 "&amp;(NUMBERSTRING(H18,1)&amp;"원정")</f>
         <v>일금 영원정</v>
       </c>
-      <c r="E18" s="90"/>
-      <c r="F18" s="90"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="99"/>
       <c r="G18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H18" s="30">
         <f>'기성금 내역서'!H29</f>
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -3316,84 +3356,84 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="90" t="str">
+        <v>18</v>
+      </c>
+      <c r="D20" s="99" t="str">
         <f>"일금 "&amp;(NUMBERSTRING(H20,1)&amp;"원정")</f>
         <v>일금 영원정</v>
       </c>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="99"/>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H20" s="30">
         <f>'기성금 내역서'!J29</f>
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="78"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
+      <c r="A21" s="52"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="81"/>
-      <c r="B22" s="82"/>
-      <c r="C22" s="83"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="84"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="84"/>
+      <c r="A22" s="55"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="90" t="str">
+        <v>18</v>
+      </c>
+      <c r="D23" s="99" t="str">
         <f>"일금 "&amp;(NUMBERSTRING(H23,1)&amp;"원정")</f>
         <v>일금 영원정</v>
       </c>
-      <c r="E23" s="90"/>
-      <c r="F23" s="90"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="99"/>
       <c r="G23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H23" s="30">
         <f>'기성금 내역서'!L29</f>
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
@@ -3402,13 +3442,13 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
@@ -3417,32 +3457,32 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="90" t="str">
+        <v>18</v>
+      </c>
+      <c r="D27" s="99" t="str">
         <f>"일금 "&amp;(NUMBERSTRING(H27,1)&amp;"원정")</f>
         <v>일금 영원정</v>
       </c>
-      <c r="E27" s="90"/>
-      <c r="F27" s="90"/>
+      <c r="E27" s="99"/>
+      <c r="F27" s="99"/>
       <c r="G27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H27" s="30">
         <f>'기성금 내역서'!F29-'기성금 내역서'!L29</f>
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
@@ -3451,16 +3491,16 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
@@ -3468,57 +3508,57 @@
       <c r="C30" s="26"/>
     </row>
     <row r="31" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="86" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31" s="86"/>
-      <c r="C31" s="86"/>
-      <c r="D31" s="86"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="86"/>
-      <c r="G31" s="86"/>
-      <c r="H31" s="86"/>
-      <c r="I31" s="86"/>
-      <c r="J31" s="86"/>
+      <c r="A31" s="95" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="95"/>
+      <c r="C31" s="95"/>
+      <c r="D31" s="95"/>
+      <c r="E31" s="95"/>
+      <c r="F31" s="95"/>
+      <c r="G31" s="95"/>
+      <c r="H31" s="95"/>
+      <c r="I31" s="95"/>
+      <c r="J31" s="95"/>
       <c r="K31" s="16"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="86"/>
-      <c r="B32" s="86"/>
-      <c r="C32" s="86"/>
-      <c r="D32" s="86"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="86"/>
-      <c r="G32" s="86"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="86"/>
-      <c r="J32" s="86"/>
+      <c r="A32" s="95"/>
+      <c r="B32" s="95"/>
+      <c r="C32" s="95"/>
+      <c r="D32" s="95"/>
+      <c r="E32" s="95"/>
+      <c r="F32" s="95"/>
+      <c r="G32" s="95"/>
+      <c r="H32" s="95"/>
+      <c r="I32" s="95"/>
+      <c r="J32" s="95"/>
       <c r="K32" s="16"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="86"/>
-      <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="86"/>
-      <c r="G33" s="86"/>
-      <c r="H33" s="86"/>
-      <c r="I33" s="86"/>
-      <c r="J33" s="86"/>
+      <c r="A33" s="95"/>
+      <c r="B33" s="95"/>
+      <c r="C33" s="95"/>
+      <c r="D33" s="95"/>
+      <c r="E33" s="95"/>
+      <c r="F33" s="95"/>
+      <c r="G33" s="95"/>
+      <c r="H33" s="95"/>
+      <c r="I33" s="95"/>
+      <c r="J33" s="95"/>
       <c r="K33" s="16"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="86"/>
-      <c r="B34" s="86"/>
-      <c r="C34" s="86"/>
-      <c r="D34" s="86"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="86"/>
-      <c r="G34" s="86"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="86"/>
-      <c r="J34" s="86"/>
+      <c r="A34" s="95"/>
+      <c r="B34" s="95"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="95"/>
+      <c r="E34" s="95"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="95"/>
+      <c r="H34" s="95"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="95"/>
       <c r="K34" s="16"/>
       <c r="L34" s="6"/>
     </row>
@@ -3538,7 +3578,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="91" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B36" s="91"/>
       <c r="C36" s="91"/>
@@ -3570,7 +3610,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="92" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B39" s="92"/>
       <c r="C39" s="92"/>
@@ -3585,7 +3625,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="92" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B40" s="92"/>
       <c r="C40" s="92"/>
@@ -3600,7 +3640,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="92" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B41" s="92"/>
       <c r="C41" s="92"/>
@@ -3622,7 +3662,7 @@
     </row>
     <row r="44" spans="1:12" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A44" s="93" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44" s="93"/>
       <c r="C44" s="93"/>
@@ -3641,11 +3681,6 @@
     <protectedRange sqref="D4 D6 D8 A2 A36 A44 D10 D12" name="범위1"/>
   </protectedRanges>
   <mergeCells count="18">
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A39:J39"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="A44:J44"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A31:J34"/>
     <mergeCell ref="D6:J6"/>
@@ -3659,6 +3694,11 @@
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="D20:F20"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A44:J44"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3677,8 +3717,8 @@
   <dimension ref="A1:P35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.75" style="2" customWidth="1"/>
-    <col min="2" max="2" width="25.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="21.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="31.375" style="2" customWidth="1"/>
     <col min="3" max="4" width="8.625" style="2" customWidth="1"/>
     <col min="5" max="12" width="11" style="2" customWidth="1"/>
     <col min="13" max="15" width="9" style="2"/>
@@ -3687,134 +3727,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="95" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
+      <c r="A1" s="101" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="102" t="str">
+      <c r="A2" s="108" t="str">
         <f>"공사명 : "&amp;갑지!D4&amp;" 중 유리공사"</f>
         <v>공사명 :  중 유리공사</v>
       </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="108"/>
+      <c r="M2" s="108"/>
     </row>
     <row r="3" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="103" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="94" t="s">
+      <c r="C3" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="94" t="s">
+      <c r="D3" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="94" t="s">
+      <c r="E3" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="100"/>
+      <c r="M3" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="94" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="94"/>
-      <c r="M3" s="100" t="s">
+    </row>
+    <row r="4" spans="1:16" ht="20.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="104"/>
+      <c r="B4" s="105"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="107"/>
+    </row>
+    <row r="5" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="40" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" ht="20.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="98"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="77" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="77" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="77" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="77" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="77" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="77" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4" s="77" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" s="77" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="101"/>
-    </row>
-    <row r="5" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="L5" s="46"/>
-      <c r="M5" s="47" t="s">
+      <c r="B5" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="L5" s="44"/>
+      <c r="M5" s="45" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
-      <c r="B6" s="19"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="60"/>
       <c r="C6" s="20"/>
       <c r="D6" s="23"/>
       <c r="E6" s="22"/>
@@ -3822,17 +3862,17 @@
         <f t="shared" ref="F6:F13" si="0">D6*E6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="109"/>
       <c r="H6" s="21">
         <f>G6*E6</f>
         <v>0</v>
       </c>
-      <c r="I6" s="22"/>
+      <c r="I6" s="109"/>
       <c r="J6" s="21">
         <f>E6*I6</f>
         <v>0</v>
       </c>
-      <c r="K6" s="22">
+      <c r="K6" s="109">
         <f>G6+I6</f>
         <v>0</v>
       </c>
@@ -3840,766 +3880,769 @@
         <f>H6+J6</f>
         <v>0</v>
       </c>
-      <c r="M6" s="48" t="e">
+      <c r="M6" s="46" t="e">
         <f>L6/F6</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
-      <c r="B7" s="19"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="60"/>
       <c r="C7" s="20"/>
       <c r="D7" s="23"/>
       <c r="E7" s="22"/>
       <c r="F7" s="21">
-        <f t="shared" ref="F7:F25" si="1">D7*E7</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="22"/>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="109"/>
       <c r="H7" s="21">
-        <f t="shared" ref="H7:H25" si="2">G7*E7</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="22"/>
+        <f t="shared" ref="H7:H13" si="1">G7*E7</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="109"/>
       <c r="J7" s="21">
-        <f t="shared" ref="J7:J25" si="3">E7*I7</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="22">
-        <f t="shared" ref="K7:K25" si="4">G7+I7</f>
+        <f t="shared" ref="J7:J13" si="2">E7*I7</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="109">
+        <f t="shared" ref="K7:K13" si="3">G7+I7</f>
         <v>0</v>
       </c>
       <c r="L7" s="22">
-        <f t="shared" ref="L7:L25" si="5">H7+J7</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="48" t="e">
-        <f t="shared" ref="M7:M25" si="6">L7/F7</f>
+        <f t="shared" ref="L7:L28" si="4">H7+J7</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="46" t="e">
+        <f t="shared" ref="M7:M13" si="5">L7/F7</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
-      <c r="B8" s="19"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="60"/>
       <c r="C8" s="20"/>
       <c r="D8" s="23"/>
       <c r="E8" s="22"/>
       <c r="F8" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="109"/>
+      <c r="H8" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="21">
+      <c r="I8" s="109"/>
+      <c r="J8" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I8" s="22"/>
-      <c r="J8" s="21">
+      <c r="K8" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K8" s="22">
+      <c r="L8" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L8" s="22">
+      <c r="M8" s="46" t="e">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="48" t="e">
-        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="37"/>
-      <c r="B9" s="19"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="60"/>
       <c r="C9" s="20"/>
       <c r="D9" s="23"/>
       <c r="E9" s="22"/>
       <c r="F9" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="110"/>
+      <c r="H9" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9" s="22"/>
-      <c r="H9" s="21">
+      <c r="I9" s="109"/>
+      <c r="J9" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I9" s="22"/>
-      <c r="J9" s="21">
+      <c r="K9" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K9" s="22">
+      <c r="L9" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L9" s="22">
+      <c r="M9" s="46" t="e">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="48" t="e">
-        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
-      <c r="B10" s="19"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="60"/>
       <c r="C10" s="20"/>
       <c r="D10" s="23"/>
       <c r="E10" s="22"/>
       <c r="F10" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="109"/>
+      <c r="H10" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G10" s="22"/>
-      <c r="H10" s="21">
+      <c r="I10" s="109"/>
+      <c r="J10" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I10" s="22"/>
-      <c r="J10" s="21">
+      <c r="K10" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K10" s="22">
+      <c r="L10" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L10" s="22">
+      <c r="M10" s="46" t="e">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="48" t="e">
-        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
-      <c r="B11" s="19"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="60"/>
       <c r="C11" s="20"/>
       <c r="D11" s="23"/>
       <c r="E11" s="22"/>
       <c r="F11" s="21">
+        <f>D11*E11</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="109"/>
+      <c r="H11" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G11" s="22"/>
-      <c r="H11" s="21">
+      <c r="I11" s="109"/>
+      <c r="J11" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I11" s="22"/>
-      <c r="J11" s="21">
+      <c r="K11" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K11" s="22">
+      <c r="L11" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L11" s="22">
+      <c r="M11" s="46" t="e">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="48" t="e">
-        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
-      <c r="B12" s="19"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="60"/>
       <c r="C12" s="20"/>
       <c r="D12" s="23"/>
       <c r="E12" s="22"/>
       <c r="F12" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="109"/>
+      <c r="H12" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="21">
+      <c r="I12" s="109"/>
+      <c r="J12" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I12" s="22"/>
-      <c r="J12" s="21">
+      <c r="K12" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K12" s="22">
+      <c r="L12" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L12" s="22">
+      <c r="M12" s="46" t="e">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="48" t="e">
-        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
-      <c r="B13" s="19"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="60"/>
       <c r="C13" s="20"/>
       <c r="D13" s="23"/>
       <c r="E13" s="22"/>
       <c r="F13" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="109"/>
+      <c r="H13" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G13" s="22"/>
-      <c r="H13" s="21">
+      <c r="I13" s="109"/>
+      <c r="J13" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I13" s="22"/>
-      <c r="J13" s="21">
+      <c r="K13" s="109">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K13" s="22">
+      <c r="L13" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L13" s="22">
+      <c r="M13" s="46" t="e">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="48" t="e">
-        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37"/>
-      <c r="B14" s="19"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="60"/>
       <c r="C14" s="20"/>
       <c r="D14" s="23"/>
       <c r="E14" s="22"/>
       <c r="F14" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="22"/>
+        <f t="shared" ref="F14:F25" si="6">D14*E14</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="109"/>
       <c r="H14" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="22"/>
+        <f t="shared" ref="H14:H25" si="7">G14*E14</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="109"/>
       <c r="J14" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="J14:J25" si="8">E14*I14</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="109">
+        <f t="shared" ref="K14:K25" si="9">G14+I14</f>
         <v>0</v>
       </c>
       <c r="L14" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="48" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L14:L25" si="10">H14+J14</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="46" t="e">
+        <f t="shared" ref="M14:M25" si="11">L14/F14</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
-      <c r="B15" s="19"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="60"/>
       <c r="C15" s="20"/>
       <c r="D15" s="23"/>
       <c r="E15" s="22"/>
       <c r="F15" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="22"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="109"/>
       <c r="H15" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="22"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="109"/>
       <c r="J15" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="109">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L15" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="48" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="46" t="e">
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
-      <c r="B16" s="19"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="60"/>
       <c r="C16" s="20"/>
       <c r="D16" s="23"/>
       <c r="E16" s="22"/>
       <c r="F16" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="22"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="109"/>
       <c r="H16" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="22"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="109"/>
       <c r="J16" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="109">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L16" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="48" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="46" t="e">
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
-      <c r="B17" s="19"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="60"/>
       <c r="C17" s="20"/>
       <c r="D17" s="23"/>
       <c r="E17" s="22"/>
       <c r="F17" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="22"/>
+        <f>D17*E17</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="109"/>
       <c r="H17" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="22"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="109"/>
       <c r="J17" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="109">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L17" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="48" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="46" t="e">
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="39"/>
-      <c r="B18" s="19"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="60"/>
       <c r="C18" s="20"/>
       <c r="D18" s="19"/>
       <c r="E18" s="21"/>
       <c r="F18" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="22"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="109"/>
       <c r="H18" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="22"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="109"/>
       <c r="J18" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="109">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L18" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="48" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="46" t="e">
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="39"/>
-      <c r="B19" s="19"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="60"/>
       <c r="C19" s="20"/>
       <c r="D19" s="19"/>
       <c r="E19" s="21"/>
       <c r="F19" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="22"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="109"/>
       <c r="H19" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="22"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="109"/>
       <c r="J19" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="109">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L19" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="48" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="46" t="e">
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="39"/>
-      <c r="B20" s="19"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="60"/>
       <c r="C20" s="20"/>
       <c r="D20" s="19"/>
       <c r="E20" s="21"/>
       <c r="F20" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="22"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="109"/>
       <c r="H20" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="22"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="109"/>
       <c r="J20" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="109">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L20" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="48" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="46" t="e">
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="39"/>
-      <c r="B21" s="19"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="60"/>
       <c r="C21" s="20"/>
       <c r="D21" s="19"/>
       <c r="E21" s="21"/>
       <c r="F21" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="22"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="109"/>
       <c r="H21" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="22"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="109"/>
       <c r="J21" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="109">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L21" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="48" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="46" t="e">
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="39"/>
-      <c r="B22" s="19"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="60"/>
       <c r="C22" s="20"/>
       <c r="D22" s="19"/>
       <c r="E22" s="21"/>
       <c r="F22" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="22"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="109"/>
       <c r="H22" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="22"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="109"/>
       <c r="J22" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="109">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L22" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="48" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="46" t="e">
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="39"/>
-      <c r="B23" s="19"/>
+      <c r="A23" s="37"/>
+      <c r="B23" s="60"/>
       <c r="C23" s="20"/>
       <c r="D23" s="19"/>
       <c r="E23" s="21"/>
       <c r="F23" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="22"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="109"/>
       <c r="H23" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="22"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="109"/>
       <c r="J23" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="109">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L23" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="48" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="46" t="e">
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="49"/>
-      <c r="B24" s="19"/>
+      <c r="A24" s="47"/>
+      <c r="B24" s="60"/>
       <c r="C24" s="20"/>
       <c r="D24" s="19"/>
       <c r="E24" s="21"/>
       <c r="F24" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="22"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="109"/>
       <c r="H24" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="22"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="109"/>
       <c r="J24" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="109">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L24" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="48" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="46" t="e">
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="50"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="51"/>
+      <c r="A25" s="48"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="49"/>
       <c r="D25" s="32"/>
       <c r="E25" s="33"/>
-      <c r="F25" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="22"/>
-      <c r="H25" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="22"/>
-      <c r="J25" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="22">
+      <c r="F25" s="33">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="111"/>
+      <c r="H25" s="33">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="111"/>
+      <c r="J25" s="33">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="111">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="34">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="50" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="62" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="65"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66">
+        <f>갑지!H16/1.1</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="67"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="66"/>
+      <c r="K26" s="67"/>
+      <c r="L26" s="67"/>
+      <c r="M26" s="68"/>
+    </row>
+    <row r="27" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="70"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="73">
+        <f>SUM(F6:F25)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="72"/>
+      <c r="H27" s="73">
+        <f>SUM(H6:H25)+F26</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="72"/>
+      <c r="J27" s="73">
+        <f>SUM(J6:J25)</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="72"/>
+      <c r="L27" s="73">
+        <f>H27+J27</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="38"/>
+    </row>
+    <row r="28" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="75"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="77">
+        <f>F27*0.1</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77">
+        <f>H27*0.1</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="77"/>
+      <c r="J28" s="77">
+        <f>J27*0.1</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="77"/>
+      <c r="L28" s="78">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L25" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="48" t="e">
-        <f t="shared" si="6"/>
+      <c r="M28" s="36"/>
+    </row>
+    <row r="29" spans="1:13" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="80"/>
+      <c r="C29" s="81"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="82"/>
+      <c r="F29" s="83">
+        <f>ROUND(F27+F28,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="82"/>
+      <c r="H29" s="83">
+        <f>ROUND(H27+H28,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="82"/>
+      <c r="J29" s="83">
+        <f>ROUND(J27+J28,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="82"/>
+      <c r="L29" s="83">
+        <f>ROUND(L27+L28,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="39" t="e">
+        <f t="shared" ref="M29" si="12">L29/F29</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="76" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C26" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="D26" s="34"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="36"/>
-      <c r="L26" s="36"/>
-      <c r="M26" s="54"/>
-    </row>
-    <row r="27" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="62"/>
-      <c r="C27" s="63"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="64"/>
-      <c r="F27" s="65">
-        <f>SUM(F6:F25)</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="64"/>
-      <c r="H27" s="65">
-        <f>SUM(H6:H25)+F26</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="64"/>
-      <c r="J27" s="65">
-        <f>SUM(J6:J25)</f>
-        <v>0</v>
-      </c>
-      <c r="K27" s="64"/>
-      <c r="L27" s="65">
-        <f>SUM(L6:L25)</f>
-        <v>0</v>
-      </c>
-      <c r="M27" s="40"/>
-    </row>
-    <row r="28" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="67"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69">
-        <f>F27*0.1</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69">
-        <f>H27*0.1</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="69"/>
-      <c r="J28" s="69">
-        <f>J27*0.1</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="69"/>
-      <c r="L28" s="70">
-        <f t="shared" ref="L7:L29" si="7">H28+J28</f>
-        <v>0</v>
-      </c>
-      <c r="M28" s="38"/>
-    </row>
-    <row r="29" spans="1:13" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="71" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" s="72"/>
-      <c r="C29" s="73"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74">
-        <f>F27+F28</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74">
-        <f>SUM(H27:H28)</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="74"/>
-      <c r="J29" s="74">
-        <f>SUM(J27:J28)</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="74"/>
-      <c r="L29" s="75">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="41" t="e">
-        <f t="shared" ref="M29" si="8">L29/F29</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
     <row r="30" spans="1:13" ht="20.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="55"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="59"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="56"/>
-      <c r="M30" s="60"/>
+      <c r="A30" s="84"/>
+      <c r="B30" s="85"/>
+      <c r="C30" s="86"/>
+      <c r="D30" s="85"/>
+      <c r="E30" s="87"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="87"/>
+      <c r="H30" s="87"/>
+      <c r="I30" s="87"/>
+      <c r="J30" s="88"/>
+      <c r="K30" s="87"/>
+      <c r="L30" s="85"/>
+      <c r="M30" s="89"/>
     </row>
     <row r="31" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
@@ -4696,6 +4739,6 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="72" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>